--- a/backend/data/Atlas_Fresh_Production_Commercial_Data.xlsx
+++ b/backend/data/Atlas_Fresh_Production_Commercial_Data.xlsx
@@ -16,14 +16,14 @@
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="174">
   <si>
     <t xml:space="preserve">Atlas Fresh — Daily Apple Export Planning</t>
   </si>
@@ -557,11 +557,12 @@
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="\€#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -577,12 +578,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -729,7 +724,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
+  <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -753,109 +748,108 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="8" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="8" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -1097,488 +1091,350 @@
   <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="31.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34.06"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="68" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="68" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+    <row r="13" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="s">
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="12" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="s">
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12" t="s">
+    <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
+    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1612,821 +1468,781 @@
   <dimension ref="A1:K1048576"/>
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="18.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="8" style="0" width="15.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="18.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="8" style="1" width="15.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="10" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="16" t="n">
         <v>0.9</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="14" t="n">
+      <c r="F5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="D6" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="J5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="17" t="n">
+      <c r="J6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D9" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="19" t="n">
         <v>0.8</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="F6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="17" t="n">
+      <c r="G10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>28</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="J12" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="14" t="n">
+      <c r="J13" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="J21" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>32</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="K23" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="I8" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>32</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>28</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>34</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="K13" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="17" t="n">
-        <v>26</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="K15" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="17" t="n">
-        <v>33</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G16" s="18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H16" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>35</v>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K17" s="14" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G18" s="18" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="K18" s="17" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>31</v>
-      </c>
-      <c r="D19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="K19" s="14" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G20" s="18" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="K20" s="17" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>28</v>
-      </c>
-      <c r="D21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="J21" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="17" t="n">
-        <v>32</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="K22" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>33</v>
-      </c>
-      <c r="D23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="K23" s="14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>27</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G24" s="18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="17" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
@@ -2450,270 +2266,250 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="24.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="24.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30.65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="20" t="n">
         <v>1500</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="22" t="n">
         <v>1450</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="20" t="n">
         <v>1250</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="22" t="n">
         <v>1200</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="20" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="F10" s="21" t="n">
+      <c r="F10" s="22" t="n">
         <v>950</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>750</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="22" t="n">
         <v>700</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="20" t="n">
         <v>1150</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="22" t="n">
         <v>900</v>
       </c>
     </row>
@@ -2740,191 +2536,151 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="22.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="22.7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="B5" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="C5" s="15" t="n">
+      <c r="B5" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="C5" s="16" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+    <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+    <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+    <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
+    <row r="13" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="20" t="n">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="21" t="n">
+      <c r="B18" s="22" t="n">
         <v>1250</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="19" t="n">
+      <c r="B19" s="20" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B20" s="21" t="n">
+      <c r="B20" s="22" t="n">
         <v>750</v>
       </c>
     </row>

--- a/backend/data/Atlas_Fresh_Production_Commercial_Data.xlsx
+++ b/backend/data/Atlas_Fresh_Production_Commercial_Data.xlsx
@@ -16,14 +16,14 @@
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="174">
   <si>
     <t xml:space="preserve">Atlas Fresh — Daily Apple Export Planning</t>
   </si>
@@ -557,12 +557,11 @@
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="\€#,##0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -578,6 +577,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -724,7 +729,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -748,108 +753,109 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="8" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="8" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -1091,350 +1097,488 @@
   <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="31.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34.06"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="B5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="B11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="68" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+    <row r="13" customFormat="false" ht="68" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="B15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
+      <c r="B16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
+      <c r="B28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="F29" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F31" s="11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="11" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-    </row>
-    <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="13" t="s">
+      <c r="B34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
+    <row r="36" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
+    <row r="37" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1465,784 +1609,821 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K1048576"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="18.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="8" style="1" width="15.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="18.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="8" style="0" width="15.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="B2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="10" t="s">
+      <c r="K4" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="15" t="n">
         <v>0.9</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="I5" s="15" t="n">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="J5" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="18" t="n">
+      <c r="B14" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="K15" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="18" t="n">
         <v>0.8</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="G16" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="F6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="18" t="n">
+      <c r="H16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="18" t="n">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="15" t="n">
+      <c r="K18" s="17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="D7" s="16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="I8" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>25</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>32</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>28</v>
-      </c>
-      <c r="D12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>34</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>26</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>20</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>33</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="C17" s="15" t="n">
-        <v>35</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K17" s="15" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>25</v>
-      </c>
-      <c r="D18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="K18" s="18" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="15" t="n">
-        <v>31</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="K19" s="15" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>29</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G20" s="19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="K20" s="18" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="C21" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="J21" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="18" t="n">
-        <v>32</v>
-      </c>
-      <c r="D22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F22" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="K22" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="15" t="n">
-        <v>33</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="K23" s="15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>27</v>
-      </c>
-      <c r="D24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G24" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="18" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
@@ -2266,250 +2447,270 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="24.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="24.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30.65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="B2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="19" t="n">
         <v>1500</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="21" t="n">
         <v>1450</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="19" t="n">
         <v>1250</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="21" t="n">
         <v>1200</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="19" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="21" t="n">
         <v>950</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="19" t="n">
         <v>750</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="21" t="n">
         <v>700</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="19" t="n">
         <v>1150</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="21" t="n">
         <v>900</v>
       </c>
     </row>
@@ -2536,151 +2737,191 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="9.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="22.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="22.7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="B2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" s="15" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="B8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+    <row r="10" customFormat="false" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+    <row r="11" customFormat="false" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+    <row r="12" customFormat="false" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+    <row r="13" customFormat="false" ht="38" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+      <c r="B15" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="19" t="n">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="21" t="n">
         <v>1250</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="19" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="21" t="n">
         <v>750</v>
       </c>
     </row>
